--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2033,6 +2033,399 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122459521</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56285</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>668485</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6617018</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122459635</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56271</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>668485</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6617018</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122459474</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56290</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>668485</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6617018</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459521</v>
+        <v>122459474</v>
       </c>
       <c r="B14" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,26 +2051,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2297,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459474</v>
+        <v>122459521</v>
       </c>
       <c r="B16" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,26 +2313,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,7 +2035,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459474</v>
+        <v>122459454</v>
       </c>
       <c r="B14" t="n">
         <v>56290</v>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459454</v>
+        <v>122459521</v>
       </c>
       <c r="B14" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,26 +2051,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2124,22 +2119,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,14 +2154,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Emily Macgregor, Torge Gerwin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459635</v>
+        <v>122459616</v>
       </c>
       <c r="B15" t="n">
         <v>56271</v>
@@ -2184,11 +2179,6 @@
       <c r="E15" t="n">
         <v>205998</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -2201,7 +2191,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2255,22 +2245,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,17 +2280,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459521</v>
+        <v>122459474</v>
       </c>
       <c r="B16" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,26 +2303,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459521</v>
+        <v>122459616</v>
       </c>
       <c r="B14" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,25 +2047,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2119,22 +2119,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,17 +2154,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emily Macgregor, Torge Gerwin</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459616</v>
+        <v>122459474</v>
       </c>
       <c r="B15" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,25 +2173,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2245,22 +2245,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459474</v>
+        <v>122459521</v>
       </c>
       <c r="B16" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,21 +2303,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Emily Macgregor, Torge Gerwin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459616</v>
+        <v>122459474</v>
       </c>
       <c r="B14" t="n">
-        <v>56271</v>
+        <v>56294</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,25 +2047,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>205995</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2119,22 +2124,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,17 +2159,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459474</v>
+        <v>122459616</v>
       </c>
       <c r="B15" t="n">
-        <v>56290</v>
+        <v>56275</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,25 +2178,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205995</v>
+        <v>205998</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2245,22 +2255,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,7 +2290,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2290,7 +2300,7 @@
         <v>122459521</v>
       </c>
       <c r="B16" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,6 +2315,11 @@
       <c r="E16" t="n">
         <v>100092</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -2406,7 +2421,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emily Macgregor, Torge Gerwin</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,7 +2035,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459474</v>
+        <v>122459454</v>
       </c>
       <c r="B14" t="n">
         <v>56294</v>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2166,7 +2166,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459616</v>
+        <v>122459635</v>
       </c>
       <c r="B15" t="n">
         <v>56275</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>119</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459454</v>
+        <v>122459616</v>
       </c>
       <c r="B14" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,25 +2047,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459635</v>
+        <v>122459521</v>
       </c>
       <c r="B15" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,30 +2178,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2297,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459521</v>
+        <v>122459474</v>
       </c>
       <c r="B16" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,26 +2313,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,7 +2035,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459616</v>
+        <v>122459635</v>
       </c>
       <c r="B14" t="n">
         <v>56275</v>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>119</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459474</v>
+        <v>122459454</v>
       </c>
       <c r="B16" t="n">
         <v>56294</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459635</v>
+        <v>122459454</v>
       </c>
       <c r="B14" t="n">
-        <v>56275</v>
+        <v>56295</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,30 +2047,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459521</v>
+        <v>122459616</v>
       </c>
       <c r="B15" t="n">
-        <v>56289</v>
+        <v>56276</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,30 +2178,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459454</v>
+        <v>122459521</v>
       </c>
       <c r="B16" t="n">
-        <v>56294</v>
+        <v>56290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,26 +2313,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459454</v>
+        <v>122459616</v>
       </c>
       <c r="B14" t="n">
-        <v>56295</v>
+        <v>56276</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,25 +2047,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459616</v>
+        <v>122459454</v>
       </c>
       <c r="B15" t="n">
-        <v>56276</v>
+        <v>56295</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,25 +2178,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,7 +2035,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459616</v>
+        <v>122459635</v>
       </c>
       <c r="B14" t="n">
         <v>56276</v>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>119</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459454</v>
+        <v>122459521</v>
       </c>
       <c r="B15" t="n">
-        <v>56295</v>
+        <v>56290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,26 +2182,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459521</v>
+        <v>122459454</v>
       </c>
       <c r="B16" t="n">
-        <v>56290</v>
+        <v>56295</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,26 +2313,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Emily Macgregor</t>
+          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459635</v>
+        <v>122459474</v>
       </c>
       <c r="B14" t="n">
-        <v>56276</v>
+        <v>56295</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,30 +2047,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459521</v>
+        <v>122459635</v>
       </c>
       <c r="B15" t="n">
-        <v>56290</v>
+        <v>56276</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,30 +2178,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>119</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2297,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459454</v>
+        <v>122459521</v>
       </c>
       <c r="B16" t="n">
-        <v>56295</v>
+        <v>56290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,26 +2313,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459616</v>
+        <v>122459454</v>
       </c>
       <c r="B14" t="n">
-        <v>56370</v>
+        <v>56389</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,25 +2047,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2297,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459454</v>
+        <v>122459616</v>
       </c>
       <c r="B16" t="n">
-        <v>56389</v>
+        <v>56370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,25 +2309,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">

--- a/artfynd/A 57943-2022 artfynd.xlsx
+++ b/artfynd/A 57943-2022 artfynd.xlsx
@@ -2035,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122459454</v>
+        <v>122459635</v>
       </c>
       <c r="B14" t="n">
-        <v>56389</v>
+        <v>56370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,30 +2047,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>119</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122459521</v>
+        <v>122459474</v>
       </c>
       <c r="B15" t="n">
-        <v>56384</v>
+        <v>56389</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,26 +2182,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2297,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122459616</v>
+        <v>122459521</v>
       </c>
       <c r="B16" t="n">
-        <v>56370</v>
+        <v>56384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,30 +2309,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Torge Gerwin, Jacqueline Nelms, David Alvunger</t>
+          <t>Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
